--- a/apps/balance-xlsx/mock-data.xlsx
+++ b/apps/balance-xlsx/mock-data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -158,6 +158,9 @@
     <t>Symbols</t>
   </si>
   <si>
+    <t>Budgets</t>
+  </si>
+  <si>
     <t>School Fees</t>
   </si>
   <si>
@@ -167,6 +170,12 @@
     <t>$</t>
   </si>
   <si>
+    <t>Monthly Budget</t>
+  </si>
+  <si>
+    <t>First Day Bias</t>
+  </si>
+  <si>
     <t>Clothes</t>
   </si>
   <si>
@@ -203,6 +212,9 @@
     <t>Loan</t>
   </si>
   <si>
+    <t>Excluded from Budget by Default</t>
+  </si>
+  <si>
     <t>Food General</t>
   </si>
   <si>
@@ -225,15 +237,6 @@
   </si>
   <si>
     <t>Medical</t>
-  </si>
-  <si>
-    <t>Budgets</t>
-  </si>
-  <si>
-    <t>Monthly Budget</t>
-  </si>
-  <si>
-    <t>First Day Bias</t>
   </si>
 </sst>
 </file>
@@ -3244,7 +3247,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -3255,7 +3258,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -3277,51 +3280,72 @@
       <c r="G2" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="I2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -3329,10 +3353,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
@@ -3340,49 +3364,67 @@
       <c r="G5" t="s">
         <v>10</v>
       </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="3">
+        <v>500</v>
+      </c>
+      <c r="K5" s="3">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="I7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="I9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3390,58 +3432,20 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="3">
-        <v>500</v>
-      </c>
-      <c r="C18" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/apps/balance-xlsx/mock-data.xlsx
+++ b/apps/balance-xlsx/mock-data.xlsx
@@ -3284,26 +3284,26 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
         <v>51</v>
       </c>
       <c r="I3" s="1" t="s">
